--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.24529958693099</v>
+        <v>1.989861182876287</v>
       </c>
       <c r="D2" t="n">
-        <v>12.40174614145189</v>
+        <v>2.015283747985933</v>
       </c>
       <c r="E2" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F2" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.85282769237018</v>
+        <v>10.53858450001016</v>
       </c>
       <c r="D3" t="n">
-        <v>64.7200622522263</v>
+        <v>10.51701011598677</v>
       </c>
       <c r="E3" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F3" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.52167436787388</v>
+        <v>8.534772084779506</v>
       </c>
       <c r="D4" t="n">
-        <v>52.18865629607339</v>
+        <v>8.480656648111927</v>
       </c>
       <c r="E4" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F4" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.052373312638</v>
+        <v>7.483510663303675</v>
       </c>
       <c r="D5" t="n">
-        <v>45.65708304427392</v>
+        <v>7.419275994694511</v>
       </c>
       <c r="E5" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F5" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.61822402628136</v>
+        <v>8.712961404270722</v>
       </c>
       <c r="D6" t="n">
-        <v>53.49396002657398</v>
+        <v>8.692768504318272</v>
       </c>
       <c r="E6" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F6" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.22998930209728</v>
+        <v>2.799873261590809</v>
       </c>
       <c r="D7" t="n">
-        <v>16.7418127492068</v>
+        <v>2.720544571746105</v>
       </c>
       <c r="E7" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F7" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.58920482933271</v>
+        <v>5.945745784766565</v>
       </c>
       <c r="D8" t="n">
-        <v>36.14655356068118</v>
+        <v>5.873814953610693</v>
       </c>
       <c r="E8" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F8" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.12294738711849</v>
+        <v>6.519978950406754</v>
       </c>
       <c r="D9" t="n">
-        <v>16.80773631397161</v>
+        <v>2.731257151020387</v>
       </c>
       <c r="E9" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F9" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.33016326478069</v>
+        <v>6.066151530526862</v>
       </c>
       <c r="D10" t="n">
-        <v>24.59879139636953</v>
+        <v>3.997303601910049</v>
       </c>
       <c r="E10" t="n">
-        <v>16.00028086577174</v>
+        <v>2.600045640687907</v>
       </c>
       <c r="F10" t="n">
-        <v>17.98810719370503</v>
+        <v>2.923067418977067</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
